--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1068,305 +1088,325 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>8.69</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-1.45</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-2.17</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>49.22</t>
-        </is>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-50.55</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.28</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-27.14</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>8493391.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>7164205.2</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>9433511.2</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>0</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-2269305</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-11840038.84784836</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-12429367.12519441</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>8493391.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>3.01</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>49.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>48.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>48.15</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1530,305 +1570,325 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>10.37</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-0.20</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>12.71</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-0.54</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>49.57</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
         <v>0</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>-30.91</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.43</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.63</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-17.94</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>10351360.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>7734892.2</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>10868737.8</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>0</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-3133845</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-11732888.25196726</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-13436063.51027082</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>10351360.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>49.35</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>49.0</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>49.3</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1992,305 +2052,325 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>4.59</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-0.71</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>12.5</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>12.76</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-1.16</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>49.93</t>
-        </is>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>49.93</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
         <v>0</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-24.23</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.51</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.68</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-11.59</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>4596491.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>9167285.6</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>15300244.2</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>0</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-6132958</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-11423220.0231848</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-14593409.89929888</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>4596491.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>49.8</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>49.8</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>49.25</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>49.35</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2454,305 +2534,325 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>5.99</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-0.60</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>15.63</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>13.12</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-0.5600000000000001</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>49.88000000000001</t>
-        </is>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>49.88000000000001</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
         <v>0</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-16.31</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.6</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.72</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-6.24</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>6038720.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>10135133.2</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>24364949.7</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>0</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-14229816</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-10846821.86389133</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-15108975.56579256</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>6038720.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>49.5</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>49.6</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2916,305 +3016,325 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>6.29</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>10.17</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>24.02</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
         <v>0</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>-9.14</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.68</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.75</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-2.41</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>6341064.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>10464020.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>32404296.7</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>0</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-21940276</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-10071884.82718202</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-15460416.21200524</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>6341064.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>49.4</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3378,305 +3498,325 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>11.21</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-0.50</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>13.56</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>49.90000000000001</t>
-        </is>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>49.90000000000001</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
         <v>0</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>-0.75</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.76</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.77</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-0.19</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>11346826.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>11702817.2</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>41428972.7</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>0</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-29726155</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-9092151.848123249</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-15442710.55616603</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>11346826.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>49.65</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -3840,305 +3980,325 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>16.88</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>48.34</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>2.28</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>49.96</t>
-        </is>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>49.96</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
         <v>0</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.83</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.77</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>17513327.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>14002583.4</v>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH8" t="n">
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL8" t="n">
         <v>0</v>
       </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-7937504.81029729</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-15402223.02796121</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>17513327.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>49.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>49.5</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4302,305 +4462,325 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>9.45</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-1.02</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-2.19</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
         <v>0</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>4.61</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.79</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-2.06</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>9435729.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>21433202.8</v>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH9" t="n">
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL9" t="n">
         <v>0</v>
       </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-6580283.316176577</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-15455000.84381285</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>9435729.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價漲量縮</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>49.0</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>49.1</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4764,305 +4944,325 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>7.60</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.50</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-3.27</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>51.38000000000001</t>
-        </is>
       </c>
       <c r="AU10" t="n">
         <v>0</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>51.38000000000001</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
         <v>0</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>24.08</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.92</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.74</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-3.19</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>7683157.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>38594766.2</v>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL10" t="n">
         <v>0</v>
       </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-4966698.311151799</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-14112976.47917903</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>7683157.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5226,305 +5426,325 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>12.40</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-1.21</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-5.23</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>52.44000000000001</t>
-        </is>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>52.44000000000001</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
         <v>0</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>46.14</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>1.02</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.7</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-9.02</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>12535047.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>54344572.8</v>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH11" t="n">
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL11" t="n">
         <v>0</v>
       </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-3303738.644237756</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-11503988.36973146</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>12535047.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>49.5</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5688,305 +5908,325 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>22.30</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-4.38</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-3.44</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>51.98999999999999</t>
-        </is>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>51.98999999999999</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
         <v>0</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>83.16</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>1.13</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.62</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-19.51</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>45011075.3</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>22845657.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>71155128.2</v>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH12" t="n">
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL12" t="n">
         <v>0</v>
       </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-1812784.148693445</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-7885851.128744528</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>22845657.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>28.32</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>87.19</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>3884</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>52.4</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>52.4</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>50.2</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>50.2</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,26 +1134,26 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,20 +1212,20 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,26 +1616,26 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.54</v>
+        <v>-2.17</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1668,14 +1668,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,20 +1694,20 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>7734892.2</v>
+        <v>7164205.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
@@ -1715,22 +1715,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1805,14 +1805,14 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,26 +2098,26 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.16</v>
+        <v>-0.54</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-30.91</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,20 +2176,20 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>9167285.6</v>
+        <v>7734892.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>15300244.2</t>
+          <t>10868737.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-6132958</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>93.037</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-58.40</t>
+          <t>-40.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,26 +2580,26 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16.31</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,20 +2658,20 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>10135133.2</v>
+        <v>9167285.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>24364949.7</t>
+          <t>15300244.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
@@ -2679,22 +2679,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-14229816</t>
+          <t>-6132958</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-11423220.0231848</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-14593409.89929888</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>127.645</t>
+          <t>121.558</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-58.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,26 +3062,26 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.88000000000001</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-16.31</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,20 +3140,20 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>10464020.6</v>
+        <v>10135133.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>32404296.7</t>
+          <t>24364949.7</t>
         </is>
       </c>
       <c r="BL6" t="n">
@@ -3161,22 +3161,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-21940276</t>
+          <t>-14229816</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-10071884.82718202</t>
+          <t>-10846821.86389133</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-15460416.21200524</t>
+          <t>-15108975.56579256</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>227.282</t>
+          <t>127.645</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,149 +3368,149 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-67.71</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-71.75</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,26 +3544,26 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>49.90000000000001</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,20 +3622,20 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>11702817.2</v>
+        <v>10464020.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>41428972.7</t>
+          <t>32404296.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-29726155</t>
+          <t>-21940276</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-9092151.848123249</t>
+          <t>-10071884.82718202</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-15442710.55616603</t>
+          <t>-15460416.21200524</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>342.246</t>
+          <t>227.282</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>2.28</v>
+        <v>-0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.90000000000001</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -4078,11 +4078,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="BD8" t="n">
         <v>0.77</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,20 +4104,20 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>14002583.4</v>
+        <v>11702817.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41428972.7</t>
         </is>
       </c>
       <c r="BL8" t="n">
@@ -4125,22 +4125,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29726155</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-7937504.81029729</t>
+          <t>-9092151.848123249</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-15402223.02796121</t>
+          <t>-15442710.55616603</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>191.634</t>
+          <t>342.246</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,26 +4508,26 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>48.34</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT9" t="n">
-        <v>-2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -4560,14 +4560,14 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,16 +4586,16 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>21433202.8</v>
+        <v>14002583.4</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -4612,17 +4612,17 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-6580283.316176577</t>
+          <t>-7937504.81029729</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-15455000.84381285</t>
+          <t>-15402223.02796121</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>154.229</t>
+          <t>191.634</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-3.27</v>
+        <v>-2.19</v>
       </c>
       <c r="AU10" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>51.38000000000001</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,16 +5068,16 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>7683157.0</t>
+          <t>9435729.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>38594766.2</v>
+        <v>21433202.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -5094,17 +5094,17 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-4966698.311151799</t>
+          <t>-6580283.316176577</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-14112976.47917903</t>
+          <t>-15455000.84381285</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>7683157.0</t>
+          <t>9435729.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>251.446</t>
+          <t>154.229</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-5.23</v>
+        <v>-3.27</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>52.44000000000001</t>
+          <t>51.38000000000001</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>46.14</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,16 +5550,16 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>12535047.0</t>
+          <t>7683157.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>54344572.8</v>
+        <v>38594766.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -5576,17 +5576,17 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3303738.644237756</t>
+          <t>-4966698.311151799</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-11503988.36973146</t>
+          <t>-14112976.47917903</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>12535047.0</t>
+          <t>7683157.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>452.148</t>
+          <t>251.446</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-3.44</v>
+        <v>-5.23</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>51.98999999999999</t>
+          <t>52.44000000000001</t>
         </is>
       </c>
       <c r="AY12" t="n">
@@ -6006,14 +6006,14 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>83.16</t>
+          <t>46.14</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-19.51</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,16 +6032,16 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>45011075.3</t>
+          <t>43104912.1875</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>22845657.0</t>
+          <t>12535047.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>71155128.2</v>
+        <v>54344572.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -6058,17 +6058,17 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1812784.148693445</t>
+          <t>-3303738.644237756</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-7885851.128744528</t>
+          <t>-11503988.36973146</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>22845657.0</t>
+          <t>12535047.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,26 +1134,26 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,20 +1212,20 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>7830987.8</v>
+        <v>7574801.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>48.1</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>48.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,26 +1616,26 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1668,14 +1668,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,20 +1694,20 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
@@ -1715,22 +1715,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,42 +1907,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-2.39</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>176.239</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>-0.1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>210.312</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,26 +2098,26 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.54</v>
+        <v>-2.17</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,20 +2176,20 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>7734892.2</v>
+        <v>7164205.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,26 +2580,26 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.16</v>
+        <v>-0.54</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-30.91</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,20 +2658,20 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>9167285.6</v>
+        <v>7734892.2</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>15300244.2</t>
+          <t>10868737.8</t>
         </is>
       </c>
       <c r="BL5" t="n">
@@ -2679,22 +2679,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-6132958</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>93.037</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,162 +2896,162 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-40.08</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>-0.71</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-58.40</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>-0.60</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,26 +3062,26 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16.31</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,20 +3140,20 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>10135133.2</v>
+        <v>9167285.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>24364949.7</t>
+          <t>15300244.2</t>
         </is>
       </c>
       <c r="BL6" t="n">
@@ -3161,22 +3161,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-14229816</t>
+          <t>-6132958</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-11423220.0231848</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-14593409.89929888</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>127.645</t>
+          <t>121.558</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-58.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,26 +3544,26 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.88000000000001</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-16.31</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,20 +3622,20 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>10464020.6</v>
+        <v>10135133.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>32404296.7</t>
+          <t>24364949.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-21940276</t>
+          <t>-14229816</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-10071884.82718202</t>
+          <t>-10846821.86389133</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-15460416.21200524</t>
+          <t>-15108975.56579256</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>227.282</t>
+          <t>127.645</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,149 +3850,149 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-3.33</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-67.71</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.89</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-71.75</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>0</t>
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,26 +4026,26 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>49.90000000000001</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,20 +4104,20 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>11702817.2</v>
+        <v>10464020.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>41428972.7</t>
+          <t>32404296.7</t>
         </is>
       </c>
       <c r="BL8" t="n">
@@ -4125,22 +4125,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-29726155</t>
+          <t>-21940276</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-9092151.848123249</t>
+          <t>-10071884.82718202</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-15442710.55616603</t>
+          <t>-15460416.21200524</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4205,24 +4205,24 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>342.246</t>
+          <t>227.282</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,17 +4508,17 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2.28</v>
+        <v>-0</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.90000000000001</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -4560,11 +4560,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="BD9" t="n">
         <v>0.77</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,20 +4586,20 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>14002583.4</v>
+        <v>11702817.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41428972.7</t>
         </is>
       </c>
       <c r="BL9" t="n">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29726155</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-7937504.81029729</t>
+          <t>-9092151.848123249</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-15402223.02796121</t>
+          <t>-15442710.55616603</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>191.634</t>
+          <t>342.246</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,26 +4990,26 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>48.34</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT10" t="n">
-        <v>-2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AU10" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,16 +5068,16 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>21433202.8</v>
+        <v>14002583.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -5094,17 +5094,17 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-6580283.316176577</t>
+          <t>-7937504.81029729</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-15455000.84381285</t>
+          <t>-15402223.02796121</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>154.229</t>
+          <t>191.634</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-3.27</v>
+        <v>-2.19</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>51.38000000000001</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,16 +5550,16 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>7683157.0</t>
+          <t>9435729.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>38594766.2</v>
+        <v>21433202.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -5576,17 +5576,17 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-4966698.311151799</t>
+          <t>-6580283.316176577</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-14112976.47917903</t>
+          <t>-15455000.84381285</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>7683157.0</t>
+          <t>9435729.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>251.446</t>
+          <t>154.229</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-5.23</v>
+        <v>-3.27</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.44000000000001</t>
+          <t>51.38000000000001</t>
         </is>
       </c>
       <c r="AY12" t="n">
@@ -6006,14 +6006,14 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>46.14</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,16 +6032,16 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>43104912.1875</t>
+          <t>40989133.85294118</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>12535047.0</t>
+          <t>7683157.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>54344572.8</v>
+        <v>38594766.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -6058,17 +6058,17 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3303738.644237756</t>
+          <t>-4966698.311151799</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-11503988.36973146</t>
+          <t>-14112976.47917903</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>12535047.0</t>
+          <t>7683157.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,26 +1134,26 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.19</v>
+        <v>-0.52</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-58.79</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,20 +1212,20 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>7574801.2</v>
+        <v>7450182.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>8308734.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,26 +1616,26 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1668,14 +1668,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,20 +1694,20 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>7830987.8</v>
+        <v>7574801.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
@@ -1715,22 +1715,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>48.1</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>48.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,26 +2098,26 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,20 +2176,20 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,26 +2580,26 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.54</v>
+        <v>-2.17</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,20 +2658,20 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>7734892.2</v>
+        <v>7164205.2</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
@@ -2679,22 +2679,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,26 +3062,26 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.16</v>
+        <v>-0.54</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-30.91</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,20 +3140,20 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9167285.6</v>
+        <v>7734892.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>15300244.2</t>
+          <t>10868737.8</t>
         </is>
       </c>
       <c r="BL6" t="n">
@@ -3161,22 +3161,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-6132958</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>93.037</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-58.40</t>
+          <t>-40.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,26 +3544,26 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16.31</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,20 +3622,20 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>10135133.2</v>
+        <v>9167285.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>24364949.7</t>
+          <t>15300244.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-14229816</t>
+          <t>-6132958</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-11423220.0231848</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-14593409.89929888</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3728,17 +3728,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>127.645</t>
+          <t>121.558</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-58.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,26 +4026,26 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.88000000000001</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-16.31</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,20 +4104,20 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>10464020.6</v>
+        <v>10135133.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>32404296.7</t>
+          <t>24364949.7</t>
         </is>
       </c>
       <c r="BL8" t="n">
@@ -4125,22 +4125,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-21940276</t>
+          <t>-14229816</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-10071884.82718202</t>
+          <t>-10846821.86389133</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-15460416.21200524</t>
+          <t>-15108975.56579256</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4205,24 +4205,24 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>227.282</t>
+          <t>127.645</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,149 +4332,149 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-3.11</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-67.71</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-3.74</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-71.75</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
       <c r="AI9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,26 +4508,26 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>49.90000000000001</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -4560,14 +4560,14 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,20 +4586,20 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>11702817.2</v>
+        <v>10464020.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>41428972.7</t>
+          <t>32404296.7</t>
         </is>
       </c>
       <c r="BL9" t="n">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-29726155</t>
+          <t>-21940276</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-9092151.848123249</t>
+          <t>-10071884.82718202</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-15442710.55616603</t>
+          <t>-15460416.21200524</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>342.246</t>
+          <t>227.282</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,17 +4990,17 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2.28</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.90000000000001</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -5042,11 +5042,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="BD10" t="n">
         <v>0.77</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,20 +5068,20 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>14002583.4</v>
+        <v>11702817.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41428972.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
@@ -5089,22 +5089,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29726155</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-7937504.81029729</t>
+          <t>-9092151.848123249</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-15402223.02796121</t>
+          <t>-15442710.55616603</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>191.634</t>
+          <t>342.246</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,26 +5472,26 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>48.34</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT11" t="n">
-        <v>-2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,16 +5550,16 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>21433202.8</v>
+        <v>14002583.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -5576,17 +5576,17 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-6580283.316176577</t>
+          <t>-7937504.81029729</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-15455000.84381285</t>
+          <t>-15402223.02796121</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>154.229</t>
+          <t>191.634</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-3.27</v>
+        <v>-2.19</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>51.38000000000001</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="AY12" t="n">
@@ -6006,14 +6006,14 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,16 +6032,16 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>40989133.85294118</t>
+          <t>39043076.16666666</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>7683157.0</t>
+          <t>9435729.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>38594766.2</v>
+        <v>21433202.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -6058,17 +6058,17 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-4966698.311151799</t>
+          <t>-6580283.316176577</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-14112976.47917903</t>
+          <t>-15455000.84381285</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>7683157.0</t>
+          <t>9435729.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV12"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -943,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -973,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,192 +1073,192 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>5.97</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>48.45</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>48.23</t>
+        </is>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-104.86</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.02</v>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-132.95</t>
+        </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+        <v>-0.08</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-58.79</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
+          <t>-69.07</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3973397.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>7450182.4</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>8308734.0</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>5849322.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>6549774.8</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>7142333.5</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
         <v>0</v>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-858551</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1273,140 +1278,145 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>3.02</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL2" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>48.1</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1425,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1550,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,147 +1605,147 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>48.68</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>48.45</t>
+        </is>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-83.70</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.06</v>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-104.86</t>
+        </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+        <v>-0.02</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-47.99</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
+          <t>-58.79</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4757787.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>7574801.2</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>8854967.2</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>3973397.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>7450182.4</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>8308734.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
         <v>0</v>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-1280165</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1755,122 +1765,122 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1880,15 +1890,20 @@
       </c>
       <c r="CT3" t="inlineStr">
         <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1907,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2032,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,147 +2092,147 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7.29</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>-0.98</v>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
       </c>
       <c r="AU4" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0</v>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>48.98</t>
-        </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>48.68</t>
+        </is>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-63.34</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.18</v>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-83.70</t>
+        </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+        <v>0.06</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-37.10</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
+          <t>-47.99</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>9674977.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>7830987.8</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>9147504.2</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>4757787.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>7574801.2</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>8854967.2</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
         <v>0</v>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-1316516</t>
-        </is>
-      </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2237,140 +2252,145 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL4" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
         <is>
           <t>48.1</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2389,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2514,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,147 +2579,147 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>11.86</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>49.22</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>48.98</t>
+        </is>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-50.55</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.28</v>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-63.34</t>
+        </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BE5" t="inlineStr">
+        <v>0.18</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BF5" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-27.14</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
+          <t>-37.10</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>8493391.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>7164205.2</v>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>9433511.2</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>9674977.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>7830987.8</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>9147504.2</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
         <v>0</v>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-2269305</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2719,140 +2739,145 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL5" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>48.0</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>48.15</t>
-        </is>
-      </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2871,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,147 +3066,147 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>12.71</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>-0.54</v>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="AU6" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0</v>
       </c>
-      <c r="AV6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-30.91</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.43</v>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-50.55</t>
+        </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BE6" t="inlineStr">
+        <v>0.28</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BF6" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-17.94</t>
-        </is>
-      </c>
       <c r="BG6" t="inlineStr">
         <is>
+          <t>-27.14</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>10351360.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>7734892.2</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>10868737.8</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>8493391.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>7164205.2</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>9433511.2</t>
+        </is>
+      </c>
+      <c r="BM6" t="n">
         <v>0</v>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-3133845</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3201,117 +3226,117 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL6" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
@@ -3321,20 +3346,25 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3353,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,147 +3553,147 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>12.76</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>-1.16</v>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>12.71</t>
+        </is>
       </c>
       <c r="AU7" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0</v>
       </c>
-      <c r="AV7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>49.93</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>49.57</t>
+        </is>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-24.23</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.51</v>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-30.91</t>
+        </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BE7" t="inlineStr">
+        <v>0.43</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BF7" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-11.59</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
+          <t>-17.94</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4596491.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9167285.6</v>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>15300244.2</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>10351360.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="n">
+        <v>7734892.2</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>10868737.8</t>
+        </is>
+      </c>
+      <c r="BM7" t="n">
         <v>0</v>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-6132958</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3683,140 +3713,145 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL7" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3835,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>93.037</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-58.40</t>
+          <t>-40.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4005,147 +4040,147 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>13.12</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>-0.5600000000000001</v>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>12.76</t>
+        </is>
       </c>
       <c r="AU8" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AV8" t="n">
         <v>0</v>
       </c>
-      <c r="AV8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>49.93</t>
+        </is>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-16.31</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.6</v>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-24.23</t>
+        </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BE8" t="inlineStr">
+        <v>0.51</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-6.24</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
+          <t>-11.59</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>6038720.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10135133.2</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>24364949.7</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>4596491.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="n">
+        <v>9167285.6</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>15300244.2</t>
+        </is>
+      </c>
+      <c r="BM8" t="n">
         <v>0</v>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-14229816</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-6132958</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-11423220.0231848</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>-14593409.89929888</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4165,140 +4200,145 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL8" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>49.35</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4317,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>127.645</t>
+          <t>121.558</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-58.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4442,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,147 +4527,147 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>24.02</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.4</v>
+          <t>15.63</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>13.12</t>
+        </is>
       </c>
       <c r="AU9" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AV9" t="n">
         <v>0</v>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>49.88000000000001</t>
+        </is>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-9.14</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.68</v>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-16.31</t>
+        </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BE9" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BF9" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>6341064.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10464020.6</v>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>32404296.7</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>6038720.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>10135133.2</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>24364949.7</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
         <v>0</v>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-21940276</t>
-        </is>
-      </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-10071884.82718202</t>
+          <t>-14229816</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-15460416.21200524</t>
+          <t>-10846821.86389133</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>-15108975.56579256</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4647,140 +4687,145 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL9" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>49.6</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4799,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>227.282</t>
+          <t>127.645</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,302 +4859,302 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.11</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-67.71</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-71.75</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>10.17</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>24.02</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>11.21</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>13.56</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>49.90000000000001</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.76</v>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-9.14</t>
+        </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BE10" t="inlineStr">
+        <v>0.68</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BF10" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
       <c r="BG10" t="inlineStr">
         <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>11346826.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11702817.2</v>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>41428972.7</t>
-        </is>
-      </c>
-      <c r="BL10" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>6341064.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>10464020.6</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>32404296.7</t>
+        </is>
+      </c>
+      <c r="BM10" t="n">
         <v>0</v>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-29726155</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-9092151.848123249</t>
+          <t>-21940276</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-15442710.55616603</t>
+          <t>-10071884.82718202</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>-15460416.21200524</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5129,59 +5174,59 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
           <t>3.11</t>
@@ -5189,80 +5234,85 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL10" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
-      </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5271,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>342.246</t>
+          <t>227.282</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5406,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,147 +5501,147 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>13.56</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT11" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0</v>
       </c>
-      <c r="AV11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>49.96</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>49.90000000000001</t>
+        </is>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.83</v>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
       </c>
       <c r="BD11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BE11" t="n">
         <v>0.77</v>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="BG11" t="inlineStr">
         <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>17513327.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>14002583.4</v>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>11346826.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>11702817.2</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>41428972.7</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
         <v>0</v>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-7937504.81029729</t>
+          <t>-29726155</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-15402223.02796121</t>
+          <t>-9092151.848123249</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>-15442710.55616603</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5611,140 +5661,145 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL11" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5763,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>191.634</t>
+          <t>342.246</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,12 +5843,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5888,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,147 +5988,147 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr">
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>48.34</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AU12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT12" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>49.96</t>
+        </is>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.79</v>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BE12" t="inlineStr">
+        <v>0.83</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BF12" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
       <c r="BG12" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>39043076.16666666</t>
-        </is>
-      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>9435729.0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>21433202.8</v>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BL12" t="n">
+          <t>37449966.0</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>17513327.0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>14002583.4</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
         <v>0</v>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-6580283.316176577</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-15455000.84381285</t>
+          <t>-7937504.81029729</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>9435729.0</t>
+          <t>-15402223.02796121</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17513327.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6093,140 +6148,145 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>-39.72456206601571</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>20.7043644669424</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>16.46354381686621</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>28.35</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
-      </c>
       <c r="CL12" t="inlineStr">
         <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="CU12" t="inlineStr">
+        <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CU12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CV12" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,42 +948,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>99.337</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>121.084</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>6549774.8</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,26 +1631,26 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.52</v>
+        <v>-0.06</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-132.95</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-69.07</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7450182.4</v>
+        <v>6549774.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8308734.0</t>
+          <t>7142333.5</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-858551</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,26 +2118,26 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.19</v>
+        <v>-0.52</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-58.79</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7574801.2</v>
+        <v>7450182.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>8308734.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2357,27 +2357,27 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,26 +2605,26 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7830987.8</v>
+        <v>7574801.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
           <t>48.1</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>48.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,26 +3092,26 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,26 +3579,26 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.54</v>
+        <v>-2.17</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7734892.2</v>
+        <v>7164205.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,26 +4066,26 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.16</v>
+        <v>-0.54</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-30.91</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>9167285.6</v>
+        <v>7734892.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>15300244.2</t>
+          <t>10868737.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-6132958</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>93.037</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-58.40</t>
+          <t>-40.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,26 +4553,26 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-16.31</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>10135133.2</v>
+        <v>9167285.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>24364949.7</t>
+          <t>15300244.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-14229816</t>
+          <t>-6132958</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-11423220.0231848</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-14593409.89929888</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4737,17 +4737,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4792,27 +4792,27 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>127.645</t>
+          <t>121.558</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-58.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,26 +5040,26 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.88000000000001</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-16.31</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>10464020.6</v>
+        <v>10135133.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>32404296.7</t>
+          <t>24364949.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-21940276</t>
+          <t>-14229816</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-10071884.82718202</t>
+          <t>-10846821.86389133</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-15460416.21200524</t>
+          <t>-15108975.56579256</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>227.282</t>
+          <t>127.645</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,149 +5346,149 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-67.71</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-71.75</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>0</t>
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,26 +5527,26 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.90000000000001</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>11702817.2</v>
+        <v>10464020.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>41428972.7</t>
+          <t>32404296.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-29726155</t>
+          <t>-21940276</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-9092151.848123249</t>
+          <t>-10071884.82718202</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-15442710.55616603</t>
+          <t>-15460416.21200524</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>342.246</t>
+          <t>227.282</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,17 +6014,17 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>2.28</v>
+        <v>-0</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.90000000000001</t>
         </is>
       </c>
       <c r="AZ12" t="n">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="BE12" t="n">
         <v>0.77</v>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>37449966.0</t>
+          <t>35939372.55</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>14002583.4</v>
+        <v>11702817.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41428972.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29726155</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-7937504.81029729</t>
+          <t>-9092151.848123249</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-15402223.02796121</t>
+          <t>-15442710.55616603</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>17513327.0</t>
+          <t>11346826.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.96</v>
+        <v>-2.91</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.88</v>
+        <v>49.96</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>5816176.2</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1435,42 +1435,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>99.337</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>121.084</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>6549774.8</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,26 +2118,26 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.52</v>
+        <v>-0.06</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-132.95</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-69.07</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7450182.4</v>
+        <v>6549774.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8308734.0</t>
+          <t>7142333.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-858551</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,26 +2605,26 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.19</v>
+        <v>-0.52</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-58.79</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7574801.2</v>
+        <v>7450182.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>8308734.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,26 +3092,26 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7830987.8</v>
+        <v>7574801.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
           <t>48.1</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>48.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,26 +3579,26 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,26 +4066,26 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.54</v>
+        <v>-2.17</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7734892.2</v>
+        <v>7164205.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,26 +4553,26 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.16</v>
+        <v>-0.54</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-30.91</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>9167285.6</v>
+        <v>7734892.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>15300244.2</t>
+          <t>10868737.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-6132958</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>93.037</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-58.40</t>
+          <t>-40.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,26 +5040,26 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-16.31</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>10135133.2</v>
+        <v>9167285.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>24364949.7</t>
+          <t>15300244.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-14229816</t>
+          <t>-6132958</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-11423220.0231848</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-14593409.89929888</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>4596491.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>127.645</t>
+          <t>121.558</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-58.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,26 +5527,26 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.88000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-16.31</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>10464020.6</v>
+        <v>10135133.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>32404296.7</t>
+          <t>24364949.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-21940276</t>
+          <t>-14229816</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-10071884.82718202</t>
+          <t>-10846821.86389133</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-15460416.21200524</t>
+          <t>-15108975.56579256</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>6341064.0</t>
+          <t>6038720.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>227.282</t>
+          <t>127.645</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,149 +5833,149 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-67.71</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-71.75</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
       <c r="AI12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,26 +6014,26 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.90000000000001</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>35939372.55</t>
+          <t>34515309.14285715</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>11702817.2</v>
+        <v>10464020.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>41428972.7</t>
+          <t>32404296.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-29726155</t>
+          <t>-21940276</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-9092151.848123249</t>
+          <t>-10071884.82718202</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-15442710.55616603</t>
+          <t>-15460416.21200524</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>11346826.0</t>
+          <t>6341064.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW12"/>
+  <dimension ref="A1:CW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,42 +948,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>78.175</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>82.495</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>-0.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.91</v>
+        <v>-1.04</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.96</v>
+        <v>49.36</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-137.72</t>
+          <t>-145.88</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-82.81</t>
+          <t>-90.36</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4685719.6</v>
+        <v>4695179.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6258353.7</t>
+          <t>6072680.9</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1572634</t>
+          <t>-1377501</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-10125932.78193872</t>
+          <t>-9117534.988165837</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-7639128.00835297</t>
+          <t>-6299015.194767015</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,14 +1333,14 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>101.052</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>74.56</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.96</v>
+        <v>-1.9</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.72000000000001</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.88</v>
+        <v>49.66</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>5816176.2</v>
+        <v>4725357.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6150079.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1424721</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-9629993.132420167</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-6902325.060068116</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,14 +1820,14 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>121.084</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,24 +2123,24 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.06</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-2.91</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>49.96</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>6549774.8</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>99.337</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,24 +2610,24 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.52</v>
+        <v>1.24</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7450182.4</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8308734.0</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-858551</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
           <t>49.1</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,21 +3097,21 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-132.95</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-69.07</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7574801.2</v>
+        <v>6549774.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>7142333.5</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,21 +3584,21 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.98</v>
+        <v>-0.52</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.18</v>
+        <v>-0.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-58.79</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7830987.8</v>
+        <v>7450182.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8308734.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
           <t>48.1</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CS7" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-2.17</v>
+        <v>-1.19</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7164205.2</v>
+        <v>7574801.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4558,21 +4558,21 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.54</v>
+        <v>-0.98</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7734892.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>93.037</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-40.08</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,21 +5045,21 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.16</v>
+        <v>-2.17</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.51</v>
+        <v>0.28</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9167285.6</v>
+        <v>7164205.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>15300244.2</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-6132958</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11423220.0231848</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-14593409.89929888</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>4596491.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>121.558</t>
+          <t>210.312</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-58.40</t>
+          <t>-28.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,21 +5532,21 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.88000000000001</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-16.31</t>
+          <t>-30.91</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>34515309.14285715</t>
+          <t>32086487.67391304</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>10135133.2</v>
+        <v>7734892.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>24364949.7</t>
+          <t>10868737.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-14229816</t>
+          <t>-3133845</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-10846821.86389133</t>
+          <t>-11732888.25196726</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-15108975.56579256</t>
+          <t>-13436063.51027082</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>6038720.0</t>
+          <t>10351360.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
+          <t>49.35</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5800,493 +5800,6 @@
         </is>
       </c>
       <c r="CW11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6614</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>127.645</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.43</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-67.71</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>6.29</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>10.17</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>24.02</t>
-        </is>
-      </c>
-      <c r="AU12" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-9.14</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>34515309.14285715</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>6341064.0</t>
-        </is>
-      </c>
-      <c r="BK12" t="n">
-        <v>10464020.6</v>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>32404296.7</t>
-        </is>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-21940276</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-10071884.82718202</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-15460416.21200524</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>6341064.0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>資拓宏宇</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>資拓宏宇</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>數位雲端</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>-39.72456206601571</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>20.7043644669424</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>16.46354381686621</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>19.08</t>
-        </is>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
-      <c r="CJ12" t="inlineStr">
-        <is>
-          <t>12.13%</t>
-        </is>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>3.14%</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>85.15</t>
-        </is>
-      </c>
-      <c r="CM12" t="inlineStr">
-        <is>
-          <t>3952</t>
-        </is>
-      </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>資拓宏宇-數位雲端-上市</t>
-        </is>
-      </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="CT12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CU12" t="inlineStr">
-        <is>
-          <t>15.98</t>
-        </is>
-      </c>
-      <c r="CV12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CW12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.36</v>
+        <v>49.22</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4695179.4</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1377501</t>
+          <t>-976572</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-9117534.988165837</t>
+          <t>-8577016.972169103</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-6299015.194767015</t>
+          <t>-5604167.884187069</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>101.052</t>
+          <t>78.175</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.17</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.99</v>
+        <v>-0.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.9</v>
+        <v>-1.04</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.72000000000001</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.66</v>
+        <v>49.36</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-145.88</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-90.36</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>4725357.6</v>
+        <v>4695179.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6150079.4</t>
+          <t>6072680.9</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1424721</t>
+          <t>-1377501</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-9629993.132420167</t>
+          <t>-9117534.988165837</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-6902325.060068116</t>
+          <t>-6299015.194767015</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>82.495</t>
+          <t>101.052</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>74.56</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.91</v>
+        <v>-1.9</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.72000000000001</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.96</v>
+        <v>49.66</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-137.72</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-82.81</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>4685719.6</v>
+        <v>4725357.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6258353.7</t>
+          <t>6150079.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1572634</t>
+          <t>-1424721</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-10125932.78193872</t>
+          <t>-9629993.132420167</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-7639128.00835297</t>
+          <t>-6902325.060068116</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
           <t>49.2</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.96</v>
+        <v>-2.91</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.88</v>
+        <v>49.96</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>5816176.2</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121.084</t>
+          <t>99.337</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>6549774.8</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,26 +3579,26 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.52</v>
+        <v>-0.06</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-132.95</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-69.07</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7450182.4</v>
+        <v>6549774.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8308734.0</t>
+          <t>7142333.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-858551</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,26 +4066,26 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.19</v>
+        <v>-0.52</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-58.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7574801.2</v>
+        <v>7450182.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>8308734.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,26 +4553,26 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7830987.8</v>
+        <v>7574801.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
           <t>48.1</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>48.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,26 +5040,26 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>210.312</t>
+          <t>176.239</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-28.83</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,26 +5527,26 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.54</v>
+        <v>-2.17</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-30.91</t>
+          <t>-50.55</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-27.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>32086487.67391304</t>
+          <t>31084336.5</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>7734892.2</v>
+        <v>7164205.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>10868737.8</t>
+          <t>9433511.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3133845</t>
+          <t>-2269305</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-11732888.25196726</t>
+          <t>-11840038.84784836</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-13436063.51027082</t>
+          <t>-12429367.12519441</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>10351360.0</t>
+          <t>8493391.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.22</v>
+        <v>49.16</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4596629.6</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.36</v>
+        <v>49.22</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>4695179.4</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1377501</t>
+          <t>-976572</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-9117534.988165837</t>
+          <t>-8577016.972169103</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-6299015.194767015</t>
+          <t>-5604167.884187069</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,14 +1820,14 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>101.052</t>
+          <t>78.175</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.17</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,24 +2123,24 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.99</v>
+        <v>-0.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.9</v>
+        <v>-1.04</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.72000000000001</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.66</v>
+        <v>49.36</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-145.88</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-90.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>4725357.6</v>
+        <v>4695179.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6150079.4</t>
+          <t>6072680.9</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1424721</t>
+          <t>-1377501</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-9629993.132420167</t>
+          <t>-9117534.988165837</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-6902325.060068116</t>
+          <t>-6299015.194767015</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>101.052</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>82.495</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,24 +2610,24 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>74.56</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.91</v>
+        <v>-1.9</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.72000000000001</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.96</v>
+        <v>49.66</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-137.72</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-82.81</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>4685719.6</v>
+        <v>4725357.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6258353.7</t>
+          <t>6150079.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1572634</t>
+          <t>-1424721</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-10125932.78193872</t>
+          <t>-9629993.132420167</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-7639128.00835297</t>
+          <t>-6902325.060068116</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
           <t>49.2</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.96</v>
+        <v>-2.91</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.88</v>
+        <v>49.96</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>5816176.2</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3383,42 +3383,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>99.337</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>121.084</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,24 +3584,24 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>6549774.8</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,21 +4071,21 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.52</v>
+        <v>-0.06</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-132.95</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-69.07</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7450182.4</v>
+        <v>6549774.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8308734.0</t>
+          <t>7142333.5</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-858551</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>81.763</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,21 +4558,21 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.19</v>
+        <v>-0.52</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-58.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7574801.2</v>
+        <v>7450182.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>8308734.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-858551</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-11336110.99422359</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9950008.95895004</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>3973397.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>199.634</t>
+          <t>98.719</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,21 +5045,21 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-83.70</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-47.99</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7830987.8</v>
+        <v>7574801.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>9147504.2</t>
+          <t>8854967.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1316516</t>
+          <t>-1280165</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11760852.33702724</t>
+          <t>-11588129.5460915</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-11325326.52751107</t>
+          <t>-10638154.19594495</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>9674977.0</t>
+          <t>4757787.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
           <t>48.1</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>48.5</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>176.239</t>
+          <t>199.634</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,21 +5532,21 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-2.17</v>
+        <v>-0.98</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-50.55</t>
+          <t>-63.34</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-27.14</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>31084336.5</t>
+          <t>30091979.16</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>7164205.2</v>
+        <v>7830987.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>9433511.2</t>
+          <t>9147504.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2269305</t>
+          <t>-1316516</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-11840038.84784836</t>
+          <t>-11760852.33702724</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-12429367.12519441</t>
+          <t>-11325326.52751107</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>8493391.0</t>
+          <t>9674977.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW11"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.04</v>
+        <v>1.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.16</v>
+        <v>49.26</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,30 +1212,30 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4468270.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.99</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.23</v>
+        <v>0.6</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,30 +1699,30 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>4596629.6</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,30 +2118,30 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AV4" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AV4" t="n">
-        <v>-1.04</v>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,30 +2186,30 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>4695179.4</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1377501</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-9117534.988165837</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-6299015.194767015</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>101.052</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.17</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.9</v>
+        <v>-0.23</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.72000000000001</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.66</v>
+        <v>49.22</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,30 +2673,30 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>4725357.6</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6150079.4</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1424721</t>
+          <t>-976572</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-9629993.132420167</t>
+          <t>-8577016.972169103</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-6902325.060068116</t>
+          <t>-5604167.884187069</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>82.495</t>
+          <t>78.175</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>-0.08</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.91</v>
+        <v>-1.04</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.96</v>
+        <v>49.36</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-137.72</t>
+          <t>-145.88</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,30 +3160,30 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-82.81</t>
+          <t>-90.36</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>4685719.6</v>
+        <v>4695179.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6258353.7</t>
+          <t>6072680.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1572634</t>
+          <t>-1377501</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-10125932.78193872</t>
+          <t>-9117534.988165837</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-7639128.00835297</t>
+          <t>-6299015.194767015</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>101.052</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>74.56</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="AV7" t="n">
-        <v>-2.96</v>
+        <v>-1.9</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.72000000000001</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.88</v>
+        <v>49.66</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,30 +3647,30 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>5816176.2</v>
+        <v>4725357.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6150079.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1424721</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-9629993.132420167</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-6902325.060068116</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121.084</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.06</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>-2.91</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>49.96</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,30 +4134,30 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>6549774.8</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>81.763</t>
+          <t>99.337</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.52</v>
+        <v>1.24</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,30 +4621,30 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7450182.4</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8308734.0</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-858551</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11336110.99422359</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-9950008.95895004</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>3973397.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>49.1</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>98.719</t>
+          <t>121.084</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,26 +5040,26 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-83.70</t>
+          <t>-132.95</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,30 +5108,30 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-69.07</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>30091979.16</t>
+          <t>29299936.05555556</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7574801.2</v>
+        <v>6549774.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8854967.2</t>
+          <t>7142333.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1280165</t>
+          <t>-592558</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11588129.5460915</t>
+          <t>-10988842.0249707</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-10638154.19594495</t>
+          <t>-9078862.694079854</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>4757787.0</t>
+          <t>5849322.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5313,493 +5313,6 @@
         </is>
       </c>
       <c r="CW10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>6614</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>199.634</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-14.39</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>9.84</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>11.86</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>7.29</t>
-        </is>
-      </c>
-      <c r="AU11" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-63.34</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-37.10</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>30091979.16</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>9674977.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="n">
-        <v>7830987.8</v>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>9147504.2</t>
-        </is>
-      </c>
-      <c r="BM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-1316516</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-11760852.33702724</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-11325326.52751107</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>9674977.0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>資拓宏宇</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>資拓宏宇</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>數位雲端</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>-39.72456206601571</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>20.7043644669424</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>16.46354381686621</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>19.08</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>28.88</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>12.13%</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>3.14%</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>85.93</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>資拓宏宇-數位雲端-上市</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CU11" t="inlineStr">
-        <is>
-          <t>15.98</t>
-        </is>
-      </c>
-      <c r="CV11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CW11" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1795,37 +1795,37 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.04</v>
+        <v>2.99</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.08</v>
+        <v>0.6</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>4468270.4</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2282,37 +2282,37 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.22</v>
+        <v>49.16</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>4596629.6</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2769,22 +2769,22 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.36</v>
+        <v>49.22</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>4695179.4</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1377501</t>
+          <t>-976572</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-9117534.988165837</t>
+          <t>-8577016.972169103</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-6299015.194767015</t>
+          <t>-5604167.884187069</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3256,22 +3256,22 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>101.052</t>
+          <t>78.175</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.17</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.99</v>
+        <v>-0.08</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.9</v>
+        <v>-1.04</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.72000000000001</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.66</v>
+        <v>49.36</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-145.88</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-90.36</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>4725357.6</v>
+        <v>4695179.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6150079.4</t>
+          <t>6072680.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1424721</t>
+          <t>-1377501</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-9629993.132420167</t>
+          <t>-9117534.988165837</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-6902325.060068116</t>
+          <t>-6299015.194767015</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>82.495</t>
+          <t>101.052</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>74.56</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2.91</v>
+        <v>-1.9</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.72000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.96</v>
+        <v>49.66</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-137.72</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-82.81</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>4685719.6</v>
+        <v>4725357.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6258353.7</t>
+          <t>6150079.4</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1572634</t>
+          <t>-1424721</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-10125932.78193872</t>
+          <t>-9629993.132420167</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-7639128.00835297</t>
+          <t>-6902325.060068116</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4230,22 +4230,22 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
           <t>49.2</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>-2.96</v>
+        <v>-2.91</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.88</v>
+        <v>49.96</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>5816176.2</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4717,22 +4717,22 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>121.084</t>
+          <t>99.337</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>49.88</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-132.95</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-76.89</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>29299936.05555556</t>
+          <t>28755974.51785714</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>6549774.8</v>
+        <v>5816176.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>7142333.5</t>
+          <t>6490190.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-592558</t>
+          <t>-674014</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-10988842.0249707</t>
+          <t>-10578079.10440886</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-9078862.694079854</t>
+          <t>-8318883.041318726</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5849322.0</t>
+          <t>4825398.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5204,22 +5204,22 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-39.72456206601571</t>
+          <t>-5.939528151834255</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>20.7043644669424</t>
+          <t>13.29799358093748</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>16.46354381686621</t>
+          <t>16.16559903147475</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU2" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.04</v>
+        <v>2.99</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.08</v>
+        <v>0.6</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>4468270.4</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.22</v>
+        <v>49.16</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>4596629.6</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.36</v>
+        <v>49.22</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>4695179.4</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1377501</t>
+          <t>-976572</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-9117534.988165837</t>
+          <t>-8577016.972169103</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-6299015.194767015</t>
+          <t>-5604167.884187069</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
       <c r="CH7" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>101.052</t>
+          <t>78.175</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.17</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.99</v>
+        <v>-0.08</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.9</v>
+        <v>-1.04</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.72000000000001</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.66</v>
+        <v>49.36</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-145.88</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-90.36</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>4725357.6</v>
+        <v>4695179.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6150079.4</t>
+          <t>6072680.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1424721</t>
+          <t>-1377501</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-9629993.132420167</t>
+          <t>-9117534.988165837</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-6902325.060068116</t>
+          <t>-6299015.194767015</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4955977.0</t>
+          <t>3822506.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>82.495</t>
+          <t>101.052</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>74.56</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AV9" t="n">
-        <v>-2.91</v>
+        <v>-1.9</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.72000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.96</v>
+        <v>49.66</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-137.72</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-82.81</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>4685719.6</v>
+        <v>4725357.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6258353.7</t>
+          <t>6150079.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1572634</t>
+          <t>-1424721</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-10125932.78193872</t>
+          <t>-9629993.132420167</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-7639128.00835297</t>
+          <t>-6902325.060068116</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4022694.0</t>
+          <t>4955977.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4802,17 +4802,17 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
           <t>49.2</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>99.337</t>
+          <t>82.495</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>-2.96</v>
+        <v>-2.91</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.88</v>
+        <v>49.96</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-137.72</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-76.89</t>
+          <t>-82.81</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>28755974.51785714</t>
+          <t>28083078.46551724</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>5816176.2</v>
+        <v>4685719.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6490190.7</t>
+          <t>6258353.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-674014</t>
+          <t>-1572634</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-10578079.10440886</t>
+          <t>-10125932.78193872</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-8318883.041318726</t>
+          <t>-7639128.00835297</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>4825398.0</t>
+          <t>4022694.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW2"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,7 +936,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>價_量;【b1】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>6614</t>
@@ -944,42 +948,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>113.149</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1064,12 +1068,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1094,12 +1098,12 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1119,56 +1123,56 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>68.18</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>36.36</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1176,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>49.18</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1192,46 +1196,46 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/12/31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26841757.5483871</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1239,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1319,100 +1323,3996 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>48.9</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>125.501</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>36.11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>21.21</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>49.84</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-81.30</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>6191635.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>9519633.199999999</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>6993951.8</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2525681</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-5024067.072238053</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-2303560.09300375</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>6191635.0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>125.082</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32.97</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>6.17</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>40.58</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>49.81</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>27.07</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-81.57</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>6161326.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>9118026.6</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>6857328.1</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>2260698</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-5518704.704826109</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-2475508.316377479</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>6161326.0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-2.18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>189.891</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>31.22</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>67.1</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>49.86</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>61.47</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>9379342.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>8957076</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>6826127.7</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>2130948</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-6072013.139089496</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-2629490.231326466</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>9379342.0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>171.415</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24.82</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>78.57</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>83.33</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>49.76</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>121.42</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-85.46</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>8665549.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>7845708.8</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>6285533.2</t>
+        </is>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1560175</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-6697926.39504641</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-3100341.458706219</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>8665549.0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>342.067</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20.51</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>16.87</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>90.48</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>49.52</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>125.15</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-89.87</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>17200314.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="n">
+        <v>7103794.4</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>5894757.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>1209037</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-7352032.747108264</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-3585781.767152071</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>17200314.0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>85.102</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-13.11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>71.43</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>78.35</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>49.12</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-63.93</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-93.04</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>4183602.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="n">
+        <v>4468270.4</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>5142223.3</t>
+        </is>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-673952</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-8036805.652554845</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-5065643.39467643</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>4183602.0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>49.45</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>49.45</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>108.771</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-17.52</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>85.1</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-77.56</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-91.93</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>5356573.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>4596629.6</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>5573202.2</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-976572</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-8577016.972169103</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-5604167.884187069</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>5356573.0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>78.175</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-22.68</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>63.64</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>75.77</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>48.84</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-145.88</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-90.36</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>26841757.5483871</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>3822506.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>4695179.4</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>6072680.9</t>
+        </is>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-1377501</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-9117534.988165837</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-6299015.194767015</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>3822506.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>28.97</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>84.1</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>3973</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>83.63</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>49.05</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>49.05</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE2" t="n">
         <v>0.16</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE4" t="n">
         <v>0.14</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,24 +2610,24 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU5" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,24 +3584,24 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,24 +4071,24 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.04</v>
+        <v>2.99</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.08</v>
+        <v>0.6</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>4468270.4</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,24 +4558,24 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.22</v>
+        <v>49.16</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>4596629.6</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.36</v>
+        <v>49.22</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26841757.5483871</t>
+          <t>26123001.84375</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>4695179.4</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,180 +5139,667 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
+          <t>-976572</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-8577016.972169103</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-5604167.884187069</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>5356573.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>82.32</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>3981</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>78.175</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-22.68</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>63.64</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>75.77</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>48.84</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-145.88</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-90.36</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>26123001.84375</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>3822506.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>4695179.4</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>6072680.9</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-1377501</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-9117534.988165837</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-6299015.194767015</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>3822506.0</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-5.939528151834255</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>13.29799358093748</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>16.16559903147475</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
-        <is>
-          <t>83.63</t>
-        </is>
-      </c>
-      <c r="CM10" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>82.32</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>3981</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>數位雲端平上市</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>49.05</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>49.05</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>48.65</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>48.8</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE3" t="n">
         <v>0.16</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE5" t="n">
         <v>0.14</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU6" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.04</v>
+        <v>2.99</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.08</v>
+        <v>0.6</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>4468270.4</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.22</v>
+        <v>49.16</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>4596629.6</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>78.175</t>
+          <t>108.771</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.36</v>
+        <v>49.22</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-145.88</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-91.93</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26123001.84375</t>
+          <t>25949635.27272727</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>4695179.4</v>
+        <v>4596629.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6072680.9</t>
+          <t>5573202.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1377501</t>
+          <t>-976572</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-9117534.988165837</t>
+          <t>-8577016.972169103</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-6299015.194767015</t>
+          <t>-5604167.884187069</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>3822506.0</t>
+          <t>5356573.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE4" t="n">
         <v>0.16</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,14 +3107,14 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE6" t="n">
         <v>0.14</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU7" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,167 +3895,167 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31.22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
           <t>-1.31</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>24.82</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>-0.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.04</v>
+        <v>2.99</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.08</v>
+        <v>0.6</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>4468270.4</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>108.771</t>
+          <t>85.102</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.35</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.22</v>
+        <v>49.16</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-63.93</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-91.93</t>
+          <t>-93.04</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>25949635.27272727</t>
+          <t>25920727.67647059</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>4596629.6</v>
+        <v>4468270.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>5573202.2</t>
+          <t>5142223.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-976572</t>
+          <t>-673952</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-8577016.972169103</t>
+          <t>-8036805.652554845</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-5604167.884187069</t>
+          <t>-5065643.39467643</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>5356573.0</t>
+          <t>4183602.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>83.27</t>
+          <t>83.13</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE2" t="n">
         <v>0.18</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE5" t="n">
         <v>0.16</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,14 +3594,14 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,11 +3631,11 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE7" t="n">
         <v>0.14</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU8" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>85.102</t>
+          <t>342.067</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>78.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.04</v>
+        <v>2.99</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.08</v>
+        <v>0.6</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-63.93</t>
+          <t>125.15</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-89.87</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>25920727.67647059</t>
+          <t>25494798.85714286</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>4468270.4</v>
+        <v>7103794.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>5142223.3</t>
+          <t>5894757.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-673952</t>
+          <t>1209037</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-8036805.652554845</t>
+          <t>-7352032.747108264</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-5065643.39467643</t>
+          <t>-3585781.767152071</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>4183602.0</t>
+          <t>17200314.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>83.13</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1098,24 +1098,24 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE2" t="n">
         <v>0.18</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1585,24 +1585,24 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE3" t="n">
         <v>0.18</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2072,24 +2072,24 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>0</t>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2123,24 +2123,24 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,24 +2559,24 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,24 +2610,24 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3046,24 +3046,24 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>0</t>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE6" t="n">
         <v>0.16</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,24 +3584,24 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4020,24 +4020,24 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>0</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,14 +4081,14 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE8" t="n">
         <v>0.14</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4507,24 +4507,24 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,24 +4558,24 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU9" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4994,24 +4994,24 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>0</t>
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>342.067</t>
+          <t>171.415</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5481,24 +5481,24 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>0</t>
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,24 +5532,24 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.22</v>
+        <v>49.26</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>125.15</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-89.87</t>
+          <t>-85.46</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>25494798.85714286</t>
+          <t>24974339.58333333</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>7103794.4</v>
+        <v>7845708.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>5894757.0</t>
+          <t>6285533.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>1209037</t>
+          <t>1560175</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-7352032.747108264</t>
+          <t>-6697926.39504641</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-3585781.767152071</t>
+          <t>-3100341.458706219</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>17200314.0</t>
+          <t>8665549.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW11"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,149 +963,149 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,15 +1196,15 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE2" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1333,14 +1333,14 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE3" t="n">
         <v>0.18</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,24 +2123,24 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE4" t="n">
         <v>0.18</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2610,24 +2610,24 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3331,27 +3331,27 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,24 +3584,24 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,11 +3631,11 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE7" t="n">
         <v>0.16</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,24 +4071,24 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,24 +4245,24 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
       <c r="CH8" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,14 +4568,14 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE9" t="n">
         <v>0.14</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4792,22 +4792,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU10" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,24 +5532,24 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>24974339.58333333</t>
+          <t>24676396.05405406</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,180 +5626,667 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
+          <t>2130948</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-6072013.139089496</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-2629490.231326466</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>9379342.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>數位雲端</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>-5.939528151834255</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>13.29799358093748</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>16.16559903147475</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>28.62</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>83.45</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>3924</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>資拓宏宇-數位雲端-上市</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>15.98</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>171.415</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>24.82</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>78.57</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>83.33</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>49.76</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>121.42</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-85.46</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>24676396.05405406</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>8665549.0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>7845708.8</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>6285533.2</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>1560175</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-6697926.39504641</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-3100341.458706219</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>8665549.0</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>資拓宏宇</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-5.939528151834255</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>13.29799358093748</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>16.16559903147475</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>3.15</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
         <is>
           <t>19.08</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>28.91</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>28.62</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>12.13%</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>3.14%</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>84.15</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>83.45</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>3924</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
         <is>
           <t>勞務81.35%、軟體和硬體產品18.65% (2024年)</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>資拓宏宇-數位雲端-上市</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>50.6</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="CT11" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="CU11" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="CW11" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>10278746</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,149 +1450,149 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,15 +1683,15 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE3" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE3" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE4" t="n">
         <v>0.18</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2282,37 +2282,37 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE5" t="n">
         <v>0.18</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2769,22 +2769,22 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3256,22 +3256,22 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3743,37 +3743,37 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE8" t="n">
         <v>0.16</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4230,37 +4230,37 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>125.501</t>
+          <t>113.149</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,11 +5092,11 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE10" t="n">
         <v>0.14</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5204,22 +5204,22 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU11" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5691,22 +5691,22 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>171.415</t>
+          <t>189.891</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,29 +6014,29 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-82.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>24676396.05405406</t>
+          <t>24335236.5</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>7845708.8</v>
+        <v>8957076</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>6285533.2</t>
+          <t>6826127.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>1560175</t>
+          <t>2130948</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-6697926.39504641</t>
+          <t>-6072013.139089496</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3100341.458706219</t>
+          <t>-2629490.231326466</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>8665549.0</t>
+          <t>9379342.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-5.939528151834255</t>
+          <t>159.8723326745163</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>13.29799358093748</t>
+          <t>-41.50444947329643</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>16.16559903147475</t>
+          <t>-2.37285614972694</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>161.496</t>
+          <t>152.781</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.63</v>
+        <v>-1.19</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.34</v>
+        <v>-1.1</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ2" t="n">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-117.48</t>
+          <t>-234.03</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-90.21</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>9120136.4</v>
+        <v>7263892.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>7971446.7</t>
+          <t>8091644.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1148689</t>
+          <t>-827751</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2057437.433692315</t>
+          <t>-1843815.924846207</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-685276.0750374608</t>
+          <t>-668897.6261926135</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>10278746</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,149 +1937,149 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,15 +2170,15 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE4" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE4" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF4" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE5" t="n">
         <v>0.18</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,24 +2784,24 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
       <c r="CH5" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE6" t="n">
         <v>0.18</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
       <c r="CH7" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE9" t="n">
         <v>0.16</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,42 +4844,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>113.149</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>125.501</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>49.25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,14 +5542,14 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,11 +5579,11 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE11" t="n">
         <v>0.14</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>189.891</t>
+          <t>125.082</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,29 +6014,29 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AU12" t="n">
         <v>-1.12</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-81.57</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>24335236.5</t>
+          <t>23994459.88461538</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>8957076</v>
+        <v>9118026.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>6826127.7</t>
+          <t>6857328.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>2130948</t>
+          <t>2260698</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-6072013.139089496</t>
+          <t>-5518704.704826109</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-2629490.231326466</t>
+          <t>-2475508.316377479</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>9379342.0</t>
+          <t>6161326.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>152.781</t>
+          <t>229.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.19</v>
+        <v>-1.26</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.1</v>
+        <v>-1.73</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.37</v>
+        <v>49.32</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-234.03</t>
+          <t>-1011.72</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-97.23</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7263892.6</v>
+        <v>7987410.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8091644.0</t>
+          <t>8568454.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-827751</t>
+          <t>-581043</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1843815.924846207</t>
+          <t>-1617225.408923161</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-668897.6261926135</t>
+          <t>-370977.5713464059</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>161.496</t>
+          <t>152.781</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.63</v>
+        <v>-1.19</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.34</v>
+        <v>-1.1</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-117.48</t>
+          <t>-234.03</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-90.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>9120136.4</v>
+        <v>7263892.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>7971446.7</t>
+          <t>8091644.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1148689</t>
+          <t>-827751</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2057437.433692315</t>
+          <t>-1843815.924846207</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-685276.0750374608</t>
+          <t>-668897.6261926135</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>10278746</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,149 +2424,149 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,15 +2657,15 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE5" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE5" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF5" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,29 +3092,29 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE6" t="n">
         <v>0.18</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,11 +3631,11 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE7" t="n">
         <v>0.18</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>51.808</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.21</v>
+        <v>-0.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.18</v>
+        <v>49.16</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,11 +5092,11 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BE10" t="n">
         <v>0.16</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7199271.2</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,42 +5331,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>113.149</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-5.12</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>125.501</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>49.25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-79.52</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>9519633.199999999</v>
+        <v>7199271.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>7151532.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4584994.008711744</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2170092.159317046</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>5598504.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>125.082</t>
+          <t>125.501</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,14 +6029,14 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49.18</v>
+        <v>49.14</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6066,11 +6066,11 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BE12" t="n">
         <v>0.14</v>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>23994459.88461538</t>
+          <t>23805588.45</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>9118026.6</v>
+        <v>9519633.199999999</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>6857328.1</t>
+          <t>6993951.8</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>2260698</t>
+          <t>2525681</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-5518704.704826109</t>
+          <t>-5024067.072238053</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-2475508.316377479</t>
+          <t>-2303560.09300375</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>6161326.0</t>
+          <t>6191635.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>229.48</t>
+          <t>81.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,35 +1144,35 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>10.37</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>48.17999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.32</v>
+        <v>49.22</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1011.72</t>
+          <t>-257.07</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-97.23</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7987410.4</v>
+        <v>7792506.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8568454.0</t>
+          <t>9035626.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-581043</t>
+          <t>-1243119</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1617225.408923161</t>
+          <t>-1294432.449475104</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-370977.5713464059</t>
+          <t>-628941.1469554342</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>152.781</t>
+          <t>185.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,35 +1631,35 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.37</v>
+        <v>49.28</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-234.03</t>
+          <t>-713.16</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-103.54</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7263892.6</v>
+        <v>8871850.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8091644.0</t>
+          <t>8901374.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-827751</t>
+          <t>-29524</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1843815.924846207</t>
+          <t>-1415430.868115044</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-668897.6261926135</t>
+          <t>-305560.8936703987</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>161.496</t>
+          <t>229.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.63</v>
+        <v>-1.26</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.34</v>
+        <v>-1.73</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.37</v>
+        <v>49.32</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-117.48</t>
+          <t>-1011.72</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.02</v>
+        <v>-0.19</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-97.23</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>9120136.4</v>
+        <v>7987410.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7971446.7</t>
+          <t>8568454.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1148689</t>
+          <t>-581043</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2057437.433692315</t>
+          <t>-1617225.408923161</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-685276.0750374608</t>
+          <t>-370977.5713464059</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>152.781</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.66</v>
+        <v>-1.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.22</v>
+        <v>-1.1</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-234.03</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-90.21</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>10278746</v>
+        <v>7263892.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>8091644.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>-827751</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-1843815.924846207</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-668897.6261926135</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,149 +2911,149 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>48.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14.41</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-2.72</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,14 +3107,14 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.93</v>
+        <v>-1.63</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.33</v>
+        <v>49.37</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>8930898.800000001</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,29 +3579,29 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.28</v>
+        <v>-1.66</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.1</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.3</v>
+        <v>49.36</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>9149497.6</v>
+        <v>10278746</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,29 +4066,29 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.7</v>
+        <v>-0.93</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.07</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.22</v>
+        <v>49.33</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="BE8" t="n">
         <v>0.18</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8919395.4</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.18</v>
+        <v>49.3</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>6822757</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.28</v>
+        <v>0.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.16</v>
+        <v>49.22</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,15 +5092,15 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0.18</v>
       </c>
-      <c r="BE10" t="n">
-        <v>0.16</v>
-      </c>
       <c r="BF10" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>5978371.4</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>113.149</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.21</v>
+        <v>0.34</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-79.52</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>7199271.2</v>
+        <v>6822757</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>7151532.8</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-4584994.008711744</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2170092.159317046</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>5598504.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,42 +5818,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>51.808</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>49.35</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-2.81</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>125.501</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>49.25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.93</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,29 +6014,29 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.18</v>
+        <v>-0.28</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.41</v>
+        <v>0.67</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.48999999999999</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-78.91</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>23805588.45</t>
+          <t>23130248.85714286</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>9519633.199999999</v>
+        <v>5978371.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>6993951.8</t>
+          <t>6912040.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>2525681</t>
+          <t>-933668</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-5024067.072238053</t>
+          <t>-4225798.215333542</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-2303560.09300375</t>
+          <t>-2250221.351753428</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>6191635.0</t>
+          <t>2561050.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.17</t>
+          <t>117.983</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>35.14</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.37</v>
+        <v>0.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.12</v>
+        <v>-2.05</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.17999999999999</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.22</v>
+        <v>49.21</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-257.07</t>
+          <t>-134.26</t>
         </is>
       </c>
       <c r="BD2" t="n">
         <v>-0.27</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-114.92</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>3903565.0</t>
+          <t>5674321.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7792506.4</v>
+        <v>7365726.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>9035626.2</t>
+          <t>8242931.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1243119</t>
+          <t>-877205</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1294432.449475104</t>
+          <t>-1204023.933491406</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-628941.1469554342</t>
+          <t>-706777.0955810724</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>3903565.0</t>
+          <t>5674321.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>47.75</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>48.5</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>48.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>185.26</t>
+          <t>81.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.19</v>
+        <v>-0.37</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.98</v>
+        <v>-2.12</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.17999999999999</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.28</v>
+        <v>49.22</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-713.16</t>
+          <t>-257.07</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-103.54</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>8927711.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>8871850.6</v>
+        <v>7792506.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8901374.7</t>
+          <t>9035626.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-29524</t>
+          <t>-1243119</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1415430.868115044</t>
+          <t>-1294432.449475104</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-305560.8936703987</t>
+          <t>-628941.1469554342</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>8927711.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>47.85</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>229.48</t>
+          <t>185.26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,35 +2118,35 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
         <is>
           <t>0</t>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.32</v>
+        <v>49.28</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1011.72</t>
+          <t>-713.16</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-97.23</t>
+          <t>-103.54</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7987410.4</v>
+        <v>8871850.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8568454.0</t>
+          <t>8901374.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-581043</t>
+          <t>-29524</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1617225.408923161</t>
+          <t>-1415430.868115044</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-370977.5713464059</t>
+          <t>-305560.8936703987</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>152.781</t>
+          <t>229.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.19</v>
+        <v>-1.26</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.1</v>
+        <v>-1.73</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.37</v>
+        <v>49.32</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-234.03</t>
+          <t>-1011.72</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-97.23</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7263892.6</v>
+        <v>7987410.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8091644.0</t>
+          <t>8568454.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-827751</t>
+          <t>-581043</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1843815.924846207</t>
+          <t>-1617225.408923161</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-668897.6261926135</t>
+          <t>-370977.5713464059</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>161.496</t>
+          <t>152.781</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.63</v>
+        <v>-1.19</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.34</v>
+        <v>-1.1</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-117.48</t>
+          <t>-234.03</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-90.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>9120136.4</v>
+        <v>7263892.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>7971446.7</t>
+          <t>8091644.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1148689</t>
+          <t>-827751</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2057437.433692315</t>
+          <t>-1843815.924846207</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-685276.0750374608</t>
+          <t>-668897.6261926135</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,14 +3594,14 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>10278746</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,149 +3885,149 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,14 +4081,14 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,15 +4118,15 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE8" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE8" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF8" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,29 +4553,29 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE9" t="n">
         <v>0.18</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,29 +5040,29 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,11 +5092,11 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE10" t="n">
         <v>0.18</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5527,29 +5527,29 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>51.808</t>
+          <t>272.71</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,29 +6014,29 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.48999999999999</t>
+          <t>49.58</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-78.91</t>
+          <t>-78.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>23130248.85714286</t>
+          <t>22790277.52325581</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>5978371.4</v>
+        <v>6822757</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>6912040.1</t>
+          <t>7889916.5</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-933668</t>
+          <t>-1067159</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-4225798.215333542</t>
+          <t>-3794450.759538391</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-2250221.351753428</t>
+          <t>-1422039.752665058</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>2561050.0</t>
+          <t>13601270.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,14 +6203,14 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
       <c r="CH12" t="inlineStr">
         <is>
           <t>19.08</t>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>117.983</t>
+          <t>86.354</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>35.14</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.62</v>
+        <v>0.27</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.05</v>
+        <v>-1.9</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.21</v>
+        <v>49.15</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-134.26</t>
+          <t>-87.37</t>
         </is>
       </c>
       <c r="BD2" t="n">
         <v>-0.27</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-114.92</t>
+          <t>-119.09</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5674321.0</t>
+          <t>4170299.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7365726.2</v>
+        <v>6727126.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8242931.3</t>
+          <t>6995509.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-877205</t>
+          <t>-268383</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1204023.933491406</t>
+          <t>-1150542.479451112</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-706777.0955810724</t>
+          <t>-856394.4822294936</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5674321.0</t>
+          <t>4170299.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81.17</t>
+          <t>117.983</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>35.14</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.37</v>
+        <v>0.62</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.12</v>
+        <v>-2.05</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.17999999999999</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.22</v>
+        <v>49.21</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-257.07</t>
+          <t>-134.26</t>
         </is>
       </c>
       <c r="BD3" t="n">
         <v>-0.27</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-114.92</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>3903565.0</t>
+          <t>5674321.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7792506.4</v>
+        <v>7365726.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>9035626.2</t>
+          <t>8242931.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1243119</t>
+          <t>-877205</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1294432.449475104</t>
+          <t>-1204023.933491406</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-628941.1469554342</t>
+          <t>-706777.0955810724</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>3903565.0</t>
+          <t>5674321.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>47.75</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
           <t>48.5</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>48.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>185.26</t>
+          <t>81.17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,24 +2123,24 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.19</v>
+        <v>-0.37</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.98</v>
+        <v>-2.12</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.17999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.28</v>
+        <v>49.22</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-713.16</t>
+          <t>-257.07</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-103.54</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>8927711.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>8871850.6</v>
+        <v>7792506.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8901374.7</t>
+          <t>9035626.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-29524</t>
+          <t>-1243119</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1415430.868115044</t>
+          <t>-1294432.449475104</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-305560.8936703987</t>
+          <t>-628941.1469554342</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>8927711.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>47.85</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>229.48</t>
+          <t>185.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,30 +2610,30 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.32</v>
+        <v>49.28</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1011.72</t>
+          <t>-713.16</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-97.23</t>
+          <t>-103.54</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7987410.4</v>
+        <v>8871850.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8568454.0</t>
+          <t>8901374.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-581043</t>
+          <t>-29524</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1617225.408923161</t>
+          <t>-1415430.868115044</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-370977.5713464059</t>
+          <t>-305560.8936703987</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>152.781</t>
+          <t>229.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.19</v>
+        <v>-1.26</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.1</v>
+        <v>-1.73</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.37</v>
+        <v>49.32</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-234.03</t>
+          <t>-1011.72</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-97.23</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7263892.6</v>
+        <v>7987410.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8091644.0</t>
+          <t>8568454.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-827751</t>
+          <t>-581043</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1843815.924846207</t>
+          <t>-1617225.408923161</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-668897.6261926135</t>
+          <t>-370977.5713464059</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>161.496</t>
+          <t>152.781</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.63</v>
+        <v>-1.19</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.34</v>
+        <v>-1.1</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-117.48</t>
+          <t>-234.03</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-90.21</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>9120136.4</v>
+        <v>7263892.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>7971446.7</t>
+          <t>8091644.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1148689</t>
+          <t>-827751</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2057437.433692315</t>
+          <t>-1843815.924846207</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-685276.0750374608</t>
+          <t>-668897.6261926135</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,167 +3895,167 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14.41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>7.96</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
           <t>-0.31</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>-1.34</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,14 +4081,14 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>10278746</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,177 +4372,177 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
         <is>
           <t>-1.34</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>-1.02</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,14 +4568,14 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,15 +4605,15 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE9" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE9" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF9" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>147.089</t>
+          <t>91.344</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,11 +5092,11 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="BE10" t="n">
         <v>0.18</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-77.06</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9149497.6</v>
+        <v>8930898.800000001</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>9334565.4</t>
+          <t>8065085.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>865813</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2895318.942567965</t>
+          <t>-2593294.277464299</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-671267.7892744709</t>
+          <t>-932158.6193941366</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>7342146.0</t>
+          <t>4505510.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>329.649</t>
+          <t>147.089</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,24 +5532,24 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.22</v>
+        <v>49.3</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -5579,11 +5579,11 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE11" t="n">
         <v>0.18</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-76.24</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,20 +5605,20 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>8919395.4</v>
+        <v>9149497.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>9018711.0</t>
+          <t>9334565.4</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-99315</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3299691.879530419</t>
+          <t>-2895318.942567965</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-578518.039486574</t>
+          <t>-671267.7892744709</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>16644518.0</t>
+          <t>7342146.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>272.71</t>
+          <t>329.649</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -6019,24 +6019,24 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49.18</v>
+        <v>49.22</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-78.28</t>
+          <t>-76.99</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>22790277.52325581</t>
+          <t>22414485.95454545</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>6822757</v>
+        <v>8919395.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>7889916.5</t>
+          <t>9018711.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -6113,22 +6113,22 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1067159</t>
+          <t>-99315</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3794450.759538391</t>
+          <t>-3299691.879530419</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-1422039.752665058</t>
+          <t>-578518.039486574</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>13601270.0</t>
+          <t>16644518.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>86.26</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/支援服務.xlsx
+++ b/Result/checksun_type/支援服務.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>86.354</t>
+          <t>162.539</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-13.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,29 +1144,29 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.27</v>
+        <v>-0.85</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.9</v>
+        <v>-1.79</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>48.20999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.15</v>
+        <v>49.09</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-87.37</t>
+          <t>-76.67</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.27</v>
+        <v>-0.32</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-119.09</t>
+          <t>-123.62</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4170299.0</t>
+          <t>7784911.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>6727126.2</v>
+        <v>6092161.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6995509.4</t>
+          <t>7039785.9</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-268383</t>
+          <t>-947624</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1150542.479451112</t>
+          <t>-1076400.696585964</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-856394.4822294936</t>
+          <t>-668620.8908276502</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4170299.0</t>
+          <t>7784911.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>117.983</t>
+          <t>86.354</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>35.14</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.62</v>
+        <v>0.27</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.05</v>
+        <v>-1.9</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.21</v>
+        <v>49.15</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-134.26</t>
+          <t>-87.37</t>
         </is>
       </c>
       <c r="BD3" t="n">
         <v>-0.27</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-114.92</t>
+          <t>-119.09</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,20 +1709,20 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>5674321.0</t>
+          <t>4170299.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7365726.2</v>
+        <v>6727126.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8242931.3</t>
+          <t>6995509.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-877205</t>
+          <t>-268383</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1204023.933491406</t>
+          <t>-1150542.479451112</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-706777.0955810724</t>
+          <t>-856394.4822294936</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>5674321.0</t>
+          <t>4170299.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>81.17</t>
+          <t>117.983</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,29 +2118,29 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>35.14</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.37</v>
+        <v>0.62</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.12</v>
+        <v>-2.05</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.17999999999999</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.22</v>
+        <v>49.21</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-257.07</t>
+          <t>-134.26</t>
         </is>
       </c>
       <c r="BD4" t="n">
         <v>-0.27</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-114.92</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,20 +2196,20 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>3903565.0</t>
+          <t>5674321.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7792506.4</v>
+        <v>7365726.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>9035626.2</t>
+          <t>8242931.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1243119</t>
+          <t>-877205</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1294432.449475104</t>
+          <t>-1204023.933491406</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-628941.1469554342</t>
+          <t>-706777.0955810724</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>3903565.0</t>
+          <t>5674321.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>47.75</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
           <t>48.5</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>48.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>185.26</t>
+          <t>81.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,29 +2605,29 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.19</v>
+        <v>-0.37</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.98</v>
+        <v>-2.12</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.17999999999999</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.28</v>
+        <v>49.22</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-713.16</t>
+          <t>-257.07</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-103.54</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,20 +2683,20 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>8927711.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>8871850.6</v>
+        <v>7792506.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8901374.7</t>
+          <t>9035626.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -2704,22 +2704,22 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-29524</t>
+          <t>-1243119</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1415430.868115044</t>
+          <t>-1294432.449475104</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-305560.8936703987</t>
+          <t>-628941.1469554342</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>8927711.0</t>
+          <t>3903565.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>47.85</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>229.48</t>
+          <t>185.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,35 +3092,35 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX6" t="inlineStr">
         <is>
           <t>0</t>
@@ -3128,11 +3128,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.32</v>
+        <v>49.28</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1011.72</t>
+          <t>-713.16</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-97.23</t>
+          <t>-103.54</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7987410.4</v>
+        <v>8871850.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8568454.0</t>
+          <t>8901374.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-581043</t>
+          <t>-29524</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1617225.408923161</t>
+          <t>-1415430.868115044</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-370977.5713464059</t>
+          <t>-305560.8936703987</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>10959735.0</t>
+          <t>8927711.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>152.781</t>
+          <t>229.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.19</v>
+        <v>-1.26</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.1</v>
+        <v>-1.73</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.37</v>
+        <v>49.32</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-234.03</t>
+          <t>-1011.72</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-97.23</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,20 +3657,20 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>7263892.6</v>
+        <v>7987410.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8091644.0</t>
+          <t>8568454.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-827751</t>
+          <t>-581043</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1843815.924846207</t>
+          <t>-1617225.408923161</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-668897.6261926135</t>
+          <t>-370977.5713464059</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>7363299.0</t>
+          <t>10959735.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>161.496</t>
+          <t>152.781</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.63</v>
+        <v>-1.19</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.34</v>
+        <v>-1.1</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-117.48</t>
+          <t>-234.03</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-90.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,20 +4144,20 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>9120136.4</v>
+        <v>7263892.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>7971446.7</t>
+          <t>8091644.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1148689</t>
+          <t>-827751</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2057437.433692315</t>
+          <t>-1843815.924846207</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-685276.0750374608</t>
+          <t>-668897.6261926135</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>7808222.0</t>
+          <t>7363299.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>190.039</t>
+          <t>161.496</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,14 +4568,14 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.36</v>
+        <v>49.37</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-57.07</t>
+          <t>-117.48</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-79.93</t>
+          <t>-84.48</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>10278746</v>
+        <v>9120136.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8128558.7</t>
+          <t>7971446.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -4652,22 +4652,22 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2150187</t>
+          <t>1148689</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2306921.317084107</t>
+          <t>-2057437.433692315</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-731870.0349930488</t>
+          <t>-685276.0750374608</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>9300286.0</t>
+          <t>7808222.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>91.344</t>
+          <t>190.039</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,149 +4859,149 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>48.65</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026/01/15</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
           <t>2025/12/08</t>
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.93</v>
+        <v>-1.66</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.33</v>
+        <v>49.36</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5092,15 +5092,15 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-57.07</t>
         </is>
       </c>
       <c r="BD10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0.15</v>
       </c>
-      <c r="BE10" t="n">
-        <v>0.18</v>
-      </c>
       <c r="BF10" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-77.06</t>
+          <t>-79.93</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,20 +5118,20 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>22414485.95454545</t>
+          <t>22175883.3</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>8930898.800000001</v>
+        <v>10278746</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8065085.0</t>
+          <t>8128558.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>865813</t>
+          <t>2150187</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2593294.277464299</t>
+          <t>-2306921.317084107</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-932158.6193941366</t>
+          <t>-731870.0349930488</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>4505510.0</t>
+          <t>9300286.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">